--- a/output/北塩原村_体系と工程の反映.xlsx
+++ b/output/北塩原村_体系と工程の反映.xlsx
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>村から受領（令和8年10月13日）</t>
+          <t>村から受領（令和8年10月13日）。修正箇所の指示書を作成（output/北塩原村_策定委員会資料_修正指示.docx）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>修正箇所を指示書として示す。重いものは工程（スケジュール表）と4町村広域の協議会・議会全員協議会の欠落</t>
+          <t>いま直せるもの4件（工程の表・表の下の注記・見込量の起点・新たに加える施策の所在）は差し替える文をそのまま載せた。村の回答を待つもの4件（手帳の出所・人口の見通し・課題8対7・パブリックコメントの期間）は保留として分けた</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">

--- a/output/北塩原村_体系と工程の反映.xlsx
+++ b/output/北塩原村_体系と工程の反映.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>国の基本指針の改正により、医療的ケア者（成人）と重症心身障害児者が支援の対象に加わりました。協議の場を４町村で共同設置し、医療的ケア児等コーディネーターを配置します。18歳到達前からの引継ぎ、家族の休息（レスパイト）、災害時の電源の確保までを一続きのものとして扱います。</t>
+          <t>国の基本指針の改正により、医療的ケア者（成人）と重症心身障害児者が支援の対象に加わりました。協議の場を４町村で共同設置し、医療的ケア児等コーディネーターを配置します。18歳到達前からの引継ぎ、家族の休息（レスパイト）、災害時の電源の確保までを一続きのものとして扱います。県が設置する医療的ケア児等支援地域協議会への参画と、同協議会に参画する医療的ケア児等支援センターの協力を得て個別避難計画を作ることも併せて進めます。</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">

--- a/output/北塩原村_体系と工程の反映.xlsx
+++ b/output/北塩原村_体系と工程の反映.xlsx
@@ -61,7 +61,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -118,11 +118,6 @@
         <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -203,9 +198,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2388,17 +2380,17 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>output/北塩原村_前回計画の評価_概要版.docx（Ａ４・2ページ）</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>案①（3本×素案・概要版＝6本）を採る場合に要る。当方は推奨していないが、村の要請があれば①から起こす</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>要請があれば</t>
+          <t>令和8年10月14日の指示により作成。数値は書き写さず、評価の件数をbuild_kitashiobara_zenkai_hyouka.py のデータから数え上げる</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>作成済み</t>
         </is>
       </c>
     </row>
@@ -2410,24 +2402,24 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>output/北塩原村_アンケート結果報告_概要版.docx（Ａ４・2ページ）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>案①を採る場合に要る。分析報告書は他メンバーの作成であるため、概要版も他メンバーの範囲となる</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>要請があれば</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="76" customHeight="1">
+          <t>令和8年10月14日の指示により作成。割合は正本 第2章7 の現物と照合している。分析報告書は他メンバーの作成であるため、確定値との照合が残る（Ｓ-36）</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>作成済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>⑥⑦について。前回計画評価とアンケート結果報告は計画の素材であり、計画が確定すればその一部（第3章・第2章7）に収まる。独立の概要版を作ると計画の概要版と内容が重複し、同じ数値が6カ所に分かれる。当方は数値を生成器に一本化して自己点検で照合しているが、成果品が6本になると照合の組合せが15通りになる。そのため推奨していない。村の要請があれば①の本体から起こす。</t>
+          <t>⑥⑦について。令和8年10月14日の指示により作成した。前回計画評価とアンケート結果報告は計画の素材であり、計画が確定すればその一部（第3章・第2章7）に収まるため、当初は推奨していなかった。同じ数値が6カ所に分かれると照合の組合せが15通りになるという懸念に対しては、概要版に数値を書き写さない形にして応じている。前回計画の評価の概要版は件数を本体の生成器のデータから数え上げ、アンケートの概要版は割合を正本 第2章7 の現物と照合している。いずれも生成のたびに確かめており、食い違えば生成が止まる。</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_体系と工程の反映.xlsx
+++ b/output/北塩原村_体系と工程の反映.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_当方の生成器の修正" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_工程（案Ａ）" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_成果品の構え" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_照会" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_概要版の体裁" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_照会" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -199,6 +200,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2439,6 +2443,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>概要版の体裁（前回計画の概要版の実測）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に「概要版については前回計画の添付ファイルを確認願います」との指示を受け、前回計画の概要版（source/現行計画/第4次障がい者計画等_概要版.pdf。令和6年3月・4頁）を実測した。当方が自分の判断で決めていた体裁のうち3点が食い違っていた（書体・本文の大きさ・基調色）。実測は kitashiobara_gaiyou_taisai.py が生成のたびにＰＤＦからやり直し、記録した値と合っていることを確かめる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>前回計画（実測）</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>当方の従前</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>当方の今回</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>根拠・考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>書体</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ＵＤデジタル教科書体（NK-R・NP-R・NP-B）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>ＢＩＺ ＵＤＰゴシック</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>UD デジタル 教科書体 NK-R</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ＰＤＦに埋め込まれた書体名。いずれもユニバーサルデザイン書体だが別の書体である。村は「ユニバーサルデザインフォントの周知・啓発」を第4次障がい者計画の課題に挙げている</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>本文の大きさ</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>9〜10ポイント（10ポイントが主）</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>9ポイント</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>10ポイント</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>頁ごとに最も多い大きさは1頁10・2頁10・3頁9・4頁10ポイント。住民向けに12ポイントとする案は前回より大きくなるため採らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>基調色</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>緑（見出しの文字 RGB(39,83,23)、表紙の帯 RGB(37,171,37)）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>濃紺 1F3864</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>緑 275317</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>当方の計画本文のデータ表は緑（2D7A57）であり、本文が緑・概要版が紺という食い違いが当方の中にあった</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>強調の色</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>ハイライト 黄 FFFF99・桃 FFCCCC・淡青 C6EFFE・淡紫 DEBDFF</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>囲み 薄い黄 FFF2CC</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>囲み 黄 FFFF99</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>前回は蛍光ペン風のハイライト。当方は囲み（枠線＋塗り）で行う。モノクロ印刷でも枠線で分かるため形は変えず、塗りの色を揃える</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>図の凡例の色</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>橙 E97132・桃 F559BD・紫 7030A0・青 0070C0</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>橙 FF7F0E ほか</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>橙 E97132 ほか</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>前回はモノクロ印刷すると凡例の区別が付かない。当方のグラフは模様又は線の種類で分ける必要がある（Ｓ-34）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>頁の寸法</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>540×780ポイント（Ｐｏｗｅｒｐｏｉｎｔ の「Ａ４」）</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Ａ４（210×297ミリメートル・Ｗｏｒｄ）</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Ａ４（210×297ミリメートル・Ｗｏｒｄ）</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>前回は Ｐｏｗｅｒｐｏｉｎｔ で作られている。Ｐｏｗｅｒｐｏｉｎｔ の「Ａ４」スライドはＡ４の紙より一回り小さく、印刷の余白を見込んだ寸法である。文字の大きさは実寸であり換算は要らない。当方は Ｗｏｒｄ で作る（計画本文と同じ形で編集できるようにする）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>節の見出し</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>帯に番号と名称を白抜き。帯の色は頁ごとに違う</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>帯に番号と名称を白抜き（1色）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>帯に番号と名称を白抜き（1色）</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>モノクロ印刷では帯の色の違いは濃淡だけになるが、番号と名称が白抜きで入っているため色がなくても読める。当方も同じ形である</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>編集</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>北塩原村住民課</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>北塩原村保健福祉課 福祉係</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>北塩原村保健福祉課 福祉係</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8月の調査票修正指示により確定した組織改編後のもの。前回のままにしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>頁数</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>4頁</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>計画素案7頁／評価2頁／アンケート2頁</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>本文を10ポイントにしたことにより増える（下記）</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>前回は「4 ＳＤＧｓとの関連」を含む4頁であった。当方は国の基本指針の見直しのポイントに差し替えている（令和8年9月16日に村と確認済み）。当方の概要版は正本に令和8年10月に加えた3節（方策・年齢到達・他計画との連携）と新たに加える施策の一覧を含むため、前回より中身が多い</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>橙は当方が直したものである。書体は前回と同じＵＤデジタル教科書体に、本文は10ポイントに、基調色は前回の見出しの文字の色の実測から作った緑に揃えた。住民向けに12ポイントとする案は、前回（9から10ポイント）より大きくなるため採らない。本文を1ポイント上げたことにより頁数が増えたため、改ページの位置を手で置くのをやめ、ブロックを順に置いて1頁に収まらなくなる手前で改ページを入れる形に改めた。計画素案の概要版は7頁から8頁になり、前回計画の評価とアンケート結果報告の概要版はそれぞれ2頁である。なお、前回の概要版は Ｐｏｗｅｒｐｏｉｎｔ で作られている。当方は Ｗｏｒｄ で作る（計画本文と同じ形で編集できるようにするため）。字の大きさは実寸であり換算は要らない。前回の図の凡例（橙・桃・紫・青）はモノクロ印刷すると区別が付かないため、当方のグラフは模様又は線の種類で分ける必要がある（Ｓ-34）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2530,12 +2851,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>概要版の体裁（低視力の方への配慮）</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>概要版を案Ｃの体系と案Ａの工程に合わせて作り直します。その際の体裁について、次の3点を決めたいと考えています。①色だけで区別しないこと。　グラフと表の区分を、色のほかに模様（ハッチング）又は　線の種類で分けます。②グレースケールで印刷しても読めること。　村の印刷はモノクロ（コピー）であるため、　色の濃淡だけで分けると区別できなくなります。③本文の字の大きさ。　計画本文は10ポイントですが、　概要版は住民に配るものであるため12ポイントを考えています。いずれも当方で作れますが、他の計画（高齢者福祉計画・こども計画）の概要版と体裁をそろえる必要があるため、そちらの体裁をご教示ください。</t>
+          <t>概要版の体裁は、前回計画の概要版（第４次障がい者計画等 概要版。令和６年３月・４頁）を実測して揃えました。書体はＵＤデジタル教科書体、本文は10ポイント、基調色は緑です。字の大きさについては、住民向けに12ポイントとする案も考えていましたが、前回が９から10ポイント（10ポイントが主）であったため10ポイントとしています。残っているのはグラフです。前回の概要版の２頁の棒グラフは、凡例を橙・桃・紫・青の４色で分けています。村の印刷はモノクロ（コピー）であるため、この形ではモノクロ印刷したときに凡例の区別が付きません。当方のグラフは、色のほかに模様（ハッチング）又は線の種類で分ける形にしたいと考えています。次の２点をご教示ください。①他の計画（高齢者福祉計画・こども計画）の概要版で、グラフをどのように分けておられるか。②前回計画の概要版と同じ色の並び（橙・桃・紫・青）を保ったうえで模様を重ねるか、色の並びも変えるか。あわせて、本文を10ポイントにしたことにより計画素案の概要版が７頁から８頁になりました。印刷の折り方と部数は村と再確認します。</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">

--- a/output/北塩原村_体系と工程の反映.xlsx
+++ b/output/北塩原村_体系と工程の反映.xlsx
@@ -1661,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1670,6 +1670,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1682,7 +1683,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>日付は kitashiobara_koutei.py に一本化している。所要日数は手で書かず、期限の間の営業日数を数えている。「―（並行）」は納品までの道筋の上に乗らない工程である。</t>
+          <t>日付は kitashiobara_koutei.py に一本化している。所要日数は手で書かず、期限の間の営業日数を数えている。「―（並行）」は納品までの道筋の上に乗らない工程である。精度「仮」の4件は出所が月又は旬までしかなく、日は営業日を数えるための仮置きである（Ｍ-125で照会）。</t>
         </is>
       </c>
     </row>
@@ -1715,6 +1716,11 @@
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>出所</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>精度</t>
         </is>
       </c>
     </row>
@@ -1747,6 +1753,11 @@
           <t>仕様書5（原典あり）</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="n">
@@ -1777,6 +1788,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -1807,6 +1823,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="n">
@@ -1837,6 +1858,11 @@
           <t>当方の想定</t>
         </is>
       </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -1867,6 +1893,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="n">
@@ -1897,6 +1928,11 @@
           <t>当方の想定</t>
         </is>
       </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -1927,6 +1963,11 @@
           <t>当方の想定</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="n">
@@ -1957,6 +1998,11 @@
           <t>当方の想定</t>
         </is>
       </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1984,7 +2030,12 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
+          <t>案Ａ（令和8年10月14日採用）は旬まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>仮</t>
         </is>
       </c>
     </row>
@@ -2017,6 +2068,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -2047,6 +2103,11 @@
           <t>案Ａ（令和8年10月14日採用）</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="10" t="n">
@@ -2077,6 +2138,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -2107,6 +2173,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="n">
@@ -2134,7 +2205,12 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
+          <t>案Ａ（令和8年10月14日採用）は旬まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>仮</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2240,12 @@
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
+          <t>案Ａ（令和8年10月14日採用）は月まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>仮</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2275,12 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
+          <t>案Ａ（令和8年10月14日採用）は月まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>仮</t>
         </is>
       </c>
     </row>
@@ -2207,8 +2293,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
